--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -813,6 +813,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127375116</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91621</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>658</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Smedsbo, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>524137</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6714625</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>127375116</v>
       </c>
       <c r="B3" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>127375116</v>
       </c>
       <c r="B3" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>127375116</v>
       </c>
       <c r="B3" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>127375116</v>
       </c>
       <c r="B3" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>127375116</v>
       </c>
       <c r="B3" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>127375116</v>
       </c>
       <c r="B3" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>127375116</v>
       </c>
       <c r="B3" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>127375116</v>
       </c>
       <c r="B3" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>127375116</v>
       </c>
       <c r="B3" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,6 +925,127 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129444714</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57568</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Smedsbo, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>523883</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6714640</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inte entoniga, det stegrande lätet.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>129444714</v>
       </c>
       <c r="B4" t="n">
-        <v>57568</v>
+        <v>57571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>129444714</v>
       </c>
       <c r="B4" t="n">
-        <v>57571</v>
+        <v>57576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>129444714</v>
       </c>
       <c r="B4" t="n">
-        <v>57576</v>
+        <v>57577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117405855</v>
+        <v>127375116</v>
       </c>
       <c r="B2" t="n">
-        <v>57303</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,61 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Smedsbo (Smedsbo), Dlr</t>
+          <t>Smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524004</v>
+        <v>524137</v>
       </c>
       <c r="R2" t="n">
-        <v>6714476</v>
+        <v>6714625</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,27 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ute på nya hygget, spelandes/födosök.</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,69 +767,91 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kalle Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kalle Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127375116</v>
+        <v>117405855</v>
       </c>
       <c r="B3" t="n">
-        <v>91648</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524137</v>
+        <v>524004</v>
       </c>
       <c r="R3" t="n">
-        <v>6714625</v>
+        <v>6714476</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +875,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ute på nya hygget, spelandes/födosök.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +904,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -930,11 +925,11 @@
         <v>129444714</v>
       </c>
       <c r="B4" t="n">
-        <v>57577</v>
+        <v>57794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1045,6 +1040,355 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128405220</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Smedsbo, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>524167</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6714589</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127374654</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>524109</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6714794</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123649906</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Smedsbo, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>524108</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6714516</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61535-2022 artfynd.xlsx
+++ b/artfynd/A 61535-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127375116</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117405855</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1040,6 +1055,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129444714</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128405220</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,6 +1293,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127374654</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1389,8 +1419,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123649906</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>